--- a/artfynd/A 47332-2025 artfynd.xlsx
+++ b/artfynd/A 47332-2025 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>83137578</v>
       </c>
       <c r="B2" t="n">
-        <v>100514</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503605.2634380198</v>
+        <v>503605</v>
       </c>
       <c r="R2" t="n">
-        <v>6511260.994266658</v>
+        <v>6511261</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -757,19 +752,9 @@
           <t>2006-02-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-02-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
